--- a/evaluation/gpt_pet.xlsx
+++ b/evaluation/gpt_pet.xlsx
@@ -333,7 +333,7 @@
     <col width="8.8" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.06464154043889171</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.07936507936507937</v>
+        <v>0.4615575396825397</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.3975939569912922</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.14242424242424245</v>
+        <v>0.5071095571095572</v>
       </c>
     </row>
     <row r="3">
@@ -381,7 +381,7 @@
         <v>0.22776870869288296</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.06666666666666665</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.12013023348079402</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.09090909090909088</v>
+        <v>0.516042780748663</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         <v>0.6680082317942931</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="6">
@@ -429,7 +429,7 @@
         <v>0.7327542951207594</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9116161616161615</v>
       </c>
     </row>
     <row r="7">
@@ -445,7 +445,7 @@
         <v>0.0</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.0</v>
+        <v>0.467741935483871</v>
       </c>
     </row>
     <row r="8">
@@ -461,7 +461,7 @@
         <v>0.7733570130087944</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="9">
@@ -477,7 +477,7 @@
         <v>0.15771305210596048</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10">
@@ -493,7 +493,7 @@
         <v>0.0</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.03333333333333334</v>
+        <v>0.35000000000000003</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>0.5198452137313996</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.13952020202020202</v>
+        <v>0.509760101010101</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>0.3313196276671509</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.3568181818181818</v>
+        <v>0.6575757575757576</v>
       </c>
     </row>
     <row r="13">
@@ -541,7 +541,7 @@
         <v>0.369382115699648</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.09722222222222222</v>
+        <v>0.4880050505050505</v>
       </c>
     </row>
     <row r="14">
@@ -557,7 +557,7 @@
         <v>0.6226121871688631</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6833333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -573,7 +573,7 @@
         <v>0.3731602740671912</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="16">
@@ -589,7 +589,7 @@
         <v>0.2959247023626196</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="17">
@@ -605,7 +605,7 @@
         <v>0.38706940315909666</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="18">
@@ -637,7 +637,7 @@
         <v>0.37283664601365796</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.2824254223251969</v>
+        <v>0.6364508064006937</v>
       </c>
     </row>
     <row r="20">
@@ -673,7 +673,7 @@
         <v>0.169041681584197</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.19999999999999996</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="22">
@@ -689,7 +689,7 @@
         <v>0.10653098097165183</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.09999999999999998</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="23">
@@ -705,7 +705,7 @@
         <v>0.582079763569027</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.625</v>
+        <v>0.7458333333333333</v>
       </c>
     </row>
     <row r="24">
@@ -721,7 +721,7 @@
         <v>0.7482695165801455</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>0.6398809523809523</v>
+        <v>0.8199404761904762</v>
       </c>
     </row>
     <row r="25">
@@ -737,7 +737,7 @@
         <v>0.633661951219954</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.06517273576097107</v>
+        <v>0.4075863678804855</v>
       </c>
     </row>
     <row r="26">
@@ -753,7 +753,7 @@
         <v>0.12390739552493286</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>0.1428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="27">
@@ -769,7 +769,7 @@
         <v>0.5637113501615687</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.8506944444444444</v>
       </c>
     </row>
     <row r="28">
@@ -785,7 +785,7 @@
         <v>0.22241680801619074</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>0.16103051629787066</v>
+        <v>0.5577879854216626</v>
       </c>
     </row>
     <row r="29">
@@ -801,7 +801,7 @@
         <v>0.394182612530914</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7916666666666667</v>
       </c>
     </row>
     <row r="30">
@@ -817,7 +817,7 @@
         <v>0.37293135466510197</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>0.55</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="31">
@@ -833,7 +833,7 @@
         <v>0.06471645749022141</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>0.014906043389015525</v>
+        <v>0.2574530216945078</v>
       </c>
     </row>
     <row r="32">
@@ -849,7 +849,7 @@
         <v>0.14068828097113115</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>0.10555555555555556</v>
+        <v>0.3821428571428571</v>
       </c>
     </row>
     <row r="33">
@@ -865,7 +865,7 @@
         <v>0.1129192205075518</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>0.1490251897860594</v>
+        <v>0.4600547635677285</v>
       </c>
     </row>
     <row r="34">
@@ -881,7 +881,7 @@
         <v>0.5500949776949183</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="35">
@@ -897,7 +897,7 @@
         <v>0.5127400440851051</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.7888888888888889</v>
       </c>
     </row>
     <row r="36">
@@ -913,7 +913,7 @@
         <v>0.27664055714952307</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>0.13168724279835395</v>
+        <v>0.465843621399177</v>
       </c>
     </row>
     <row r="37">
@@ -929,7 +929,7 @@
         <v>0.0</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>0.018518518518518514</v>
+        <v>0.32633242999096657</v>
       </c>
     </row>
     <row r="38">
@@ -945,7 +945,7 @@
         <v>0.22530022811809994</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="39">
@@ -961,7 +961,7 @@
         <v>0.1915609682512433</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>0.0625</v>
+        <v>0.40625</v>
       </c>
     </row>
     <row r="40">
@@ -977,7 +977,7 @@
         <v>0.0</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>0.0</v>
+        <v>0.3064516129032258</v>
       </c>
     </row>
     <row r="41">
@@ -993,7 +993,7 @@
         <v>0.8030320640514111</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>0.5902856691919189</v>
+        <v>0.7747346713306533</v>
       </c>
     </row>
     <row r="42">
@@ -1009,7 +1009,7 @@
         <v>0.4741700875342542</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.7324929971988796</v>
       </c>
     </row>
     <row r="43">
@@ -1025,7 +1025,7 @@
         <v>0.58291281191333</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>0.14814814814814814</v>
+        <v>0.4740740740740741</v>
       </c>
     </row>
     <row r="44">
@@ -1041,7 +1041,7 @@
         <v>0.7026559828077152</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="45">

--- a/evaluation/gpt_pet.xlsx
+++ b/evaluation/gpt_pet.xlsx
@@ -333,7 +333,7 @@
     <col width="8.8" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.06464154043889171</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.4615575396825397</v>
+        <v>0.06696428571428573</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.3975939569912922</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.5071095571095572</v>
+        <v>0.1241647241647242</v>
       </c>
     </row>
     <row r="3">
@@ -381,7 +381,7 @@
         <v>0.22776870869288296</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.06666666666666665</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.12013023348079402</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.516042780748663</v>
+        <v>0.08556149732620319</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         <v>0.6680082317942931</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
@@ -429,7 +429,7 @@
         <v>0.7327542951207594</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.9116161616161615</v>
+        <v>0.8299663299663299</v>
       </c>
     </row>
     <row r="7">
@@ -445,7 +445,7 @@
         <v>0.0</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.467741935483871</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -461,7 +461,7 @@
         <v>0.7733570130087944</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9">
@@ -477,7 +477,7 @@
         <v>0.15771305210596048</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="10">
@@ -493,7 +493,7 @@
         <v>0.0</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.35000000000000003</v>
+        <v>0.02222222222222223</v>
       </c>
     </row>
     <row r="11">
@@ -509,7 +509,7 @@
         <v>0.5198452137313996</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.509760101010101</v>
+        <v>0.12277777777777778</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>0.3313196276671509</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.6575757575757576</v>
+        <v>0.3419507575757576</v>
       </c>
     </row>
     <row r="13">
@@ -541,7 +541,7 @@
         <v>0.369382115699648</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.4880050505050505</v>
+        <v>0.08543771043771044</v>
       </c>
     </row>
     <row r="14">
@@ -557,7 +557,7 @@
         <v>0.6226121871688631</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.43333333333333335</v>
       </c>
     </row>
     <row r="15">
@@ -573,7 +573,7 @@
         <v>0.3731602740671912</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
@@ -589,7 +589,7 @@
         <v>0.2959247023626196</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.4285714285714286</v>
       </c>
     </row>
     <row r="17">
@@ -605,7 +605,7 @@
         <v>0.38706940315909666</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
@@ -637,7 +637,7 @@
         <v>0.37283664601365796</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.6364508064006937</v>
+        <v>0.2797356563982903</v>
       </c>
     </row>
     <row r="20">
@@ -673,7 +673,7 @@
         <v>0.169041681584197</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.6</v>
+        <v>0.19999999999999996</v>
       </c>
     </row>
     <row r="22">
@@ -689,7 +689,7 @@
         <v>0.10653098097165183</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.55</v>
+        <v>0.09999999999999998</v>
       </c>
     </row>
     <row r="23">
@@ -705,7 +705,7 @@
         <v>0.582079763569027</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>0.7458333333333333</v>
+        <v>0.5416666666666667</v>
       </c>
     </row>
     <row r="24">
@@ -721,7 +721,7 @@
         <v>0.7482695165801455</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>0.8199404761904762</v>
+        <v>0.6398809523809523</v>
       </c>
     </row>
     <row r="25">
@@ -737,7 +737,7 @@
         <v>0.633661951219954</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>0.4075863678804855</v>
+        <v>0.048879551820728305</v>
       </c>
     </row>
     <row r="26">
@@ -753,7 +753,7 @@
         <v>0.12390739552493286</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1428571428571429</v>
       </c>
     </row>
     <row r="27">
@@ -769,7 +769,7 @@
         <v>0.5637113501615687</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>0.8506944444444444</v>
+        <v>0.7013888888888888</v>
       </c>
     </row>
     <row r="28">
@@ -785,7 +785,7 @@
         <v>0.22241680801619074</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>0.5577879854216626</v>
+        <v>0.1537109473752402</v>
       </c>
     </row>
     <row r="29">
@@ -801,7 +801,7 @@
         <v>0.394182612530914</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="30">
@@ -817,7 +817,7 @@
         <v>0.37293135466510197</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>0.775</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="31">
@@ -833,7 +833,7 @@
         <v>0.06471645749022141</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>0.2574530216945078</v>
+        <v>0.007453021694507763</v>
       </c>
     </row>
     <row r="32">
@@ -849,7 +849,7 @@
         <v>0.14068828097113115</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>0.3821428571428571</v>
+        <v>0.06953262786596119</v>
       </c>
     </row>
     <row r="33">
@@ -865,7 +865,7 @@
         <v>0.1129192205075518</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>0.4600547635677285</v>
+        <v>0.11491098971455183</v>
       </c>
     </row>
     <row r="34">
@@ -881,7 +881,7 @@
         <v>0.5500949776949183</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666667</v>
       </c>
     </row>
     <row r="35">
@@ -897,7 +897,7 @@
         <v>0.5127400440851051</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>0.7888888888888889</v>
+        <v>0.5777777777777777</v>
       </c>
     </row>
     <row r="36">
@@ -913,7 +913,7 @@
         <v>0.27664055714952307</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>0.465843621399177</v>
+        <v>0.10534979423868317</v>
       </c>
     </row>
     <row r="37">
@@ -929,7 +929,7 @@
         <v>0.0</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>0.32633242999096657</v>
+        <v>0.011743450767841009</v>
       </c>
     </row>
     <row r="38">
@@ -945,7 +945,7 @@
         <v>0.22530022811809994</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>0.6428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="39">
@@ -961,7 +961,7 @@
         <v>0.1915609682512433</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>0.40625</v>
+        <v>0.046875</v>
       </c>
     </row>
     <row r="40">
@@ -977,7 +977,7 @@
         <v>0.0</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>0.3064516129032258</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41">
@@ -993,7 +993,7 @@
         <v>0.8030320640514111</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>0.7747346713306533</v>
+        <v>0.5661923765718406</v>
       </c>
     </row>
     <row r="42">
@@ -1009,7 +1009,7 @@
         <v>0.4741700875342542</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>0.7324929971988796</v>
+        <v>0.49299719887955185</v>
       </c>
     </row>
     <row r="43">
@@ -1025,7 +1025,7 @@
         <v>0.58291281191333</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>0.4740740740740741</v>
+        <v>0.11851851851851852</v>
       </c>
     </row>
     <row r="44">
@@ -1041,7 +1041,7 @@
         <v>0.7026559828077152</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="45">
